--- a/datosIntentosSin0CorValues.xlsx
+++ b/datosIntentosSin0CorValues.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,6 +519,16 @@
           <t>Num errores por tiempo excedido</t>
         </is>
       </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>% Aciertos</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>% Mal</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -580,6 +590,12 @@
       <c r="S2" t="n">
         <v>0.0212367093938484</v>
       </c>
+      <c r="T2" t="n">
+        <v>-0.01695044857464916</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.01695044857464909</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -641,6 +657,12 @@
       <c r="S3" t="n">
         <v>0.08450670755452835</v>
       </c>
+      <c r="T3" t="n">
+        <v>0.02221534648628016</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-0.02221534648628022</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -702,6 +724,12 @@
       <c r="S4" t="n">
         <v>-0.08269751379030149</v>
       </c>
+      <c r="T4" t="n">
+        <v>-0.008792355749321655</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.008792355749321752</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -763,6 +791,12 @@
       <c r="S5" t="n">
         <v>0.2636804045542149</v>
       </c>
+      <c r="T5" t="n">
+        <v>0.1047993160236831</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.1047993160236831</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -824,6 +858,12 @@
       <c r="S6" t="n">
         <v>-0.5310197850127056</v>
       </c>
+      <c r="T6" t="n">
+        <v>0.7570039967747042</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.757003996774704</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -885,6 +925,12 @@
       <c r="S7" t="n">
         <v>-0.01847686594378495</v>
       </c>
+      <c r="T7" t="n">
+        <v>0.05180390963722757</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.05180390963722779</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -946,6 +992,12 @@
       <c r="S8" t="n">
         <v>-0.08642272026509196</v>
       </c>
+      <c r="T8" t="n">
+        <v>0.4361915413853884</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.4361915413853885</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1007,6 +1059,12 @@
       <c r="S9" t="n">
         <v>0.1151197864942924</v>
       </c>
+      <c r="T9" t="n">
+        <v>-0.6672162627581879</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.6672162627581878</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1068,6 +1126,12 @@
       <c r="S10" t="n">
         <v>0.04049716771230077</v>
       </c>
+      <c r="T10" t="n">
+        <v>0.1156934505366746</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.1156934505366749</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1129,6 +1193,12 @@
       <c r="S11" t="n">
         <v>-0.08638218150275641</v>
       </c>
+      <c r="T11" t="n">
+        <v>0.314112906428198</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.3141129064281983</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1190,6 +1260,12 @@
       <c r="S12" t="n">
         <v>0.2746470265852904</v>
       </c>
+      <c r="T12" t="n">
+        <v>-0.4132014179334478</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.4132014179334478</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1251,6 +1327,12 @@
       <c r="S13" t="n">
         <v>-0.04403828573766053</v>
       </c>
+      <c r="T13" t="n">
+        <v>0.007051032010473943</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.007051032010474103</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1312,6 +1394,12 @@
       <c r="S14" t="n">
         <v>-0.06212014841486409</v>
       </c>
+      <c r="T14" t="n">
+        <v>0.3848170572624721</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0.3848170572624721</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1373,6 +1461,12 @@
       <c r="S15" t="n">
         <v>0.0139881749987461</v>
       </c>
+      <c r="T15" t="n">
+        <v>-0.5698753053510365</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.5698753053510361</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1434,6 +1528,12 @@
       <c r="S16" t="n">
         <v>0.08547403458041188</v>
       </c>
+      <c r="T16" t="n">
+        <v>0.2315273097582529</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.231527309758253</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1495,6 +1595,12 @@
       <c r="S17" t="n">
         <v>-0.1656620751616632</v>
       </c>
+      <c r="T17" t="n">
+        <v>0.1829556233367393</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0.1829556233367393</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1556,6 +1662,12 @@
       <c r="S18" t="n">
         <v>0.9273300782870121</v>
       </c>
+      <c r="T18" t="n">
+        <v>-0.05014699650174353</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.05014699650174356</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1615,6 +1727,146 @@
         <v>0.9273300782870121</v>
       </c>
       <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.1527061016605243</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.1527061016605243</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>% Aciertos</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>-0.01695044857464916</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.02221534648628016</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.008792355749321655</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.1047993160236831</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.7570039967747042</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05180390963722757</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.4361915413853884</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.6672162627581879</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.1156934505366746</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.314112906428198</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.4132014179334478</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.007051032010473943</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.3848170572624721</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-0.5698753053510365</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.2315273097582529</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.1829556233367393</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-0.05014699650174353</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-0.1527061016605243</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>% Mal</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.01695044857464909</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.02221534648628022</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.008792355749321752</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.1047993160236831</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.757003996774704</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.05180390963722779</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.4361915413853885</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.6672162627581878</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-0.1156934505366749</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.3141129064281983</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.4132014179334478</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-0.007051032010474103</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-0.3848170572624721</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.5698753053510361</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.231527309758253</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-0.1829556233367393</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.05014699650174356</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.1527061016605243</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U21" t="n">
         <v>1</v>
       </c>
     </row>
